--- a/review_test_cases/14_edge_case_test_problem/eage_case.xlsx
+++ b/review_test_cases/14_edge_case_test_problem/eage_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HydrogenRb\HydrogenRb\Work\tech\Agent\8_14\review_test_cases\14_edge_case_test_problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7393D316-4D41-4A53-A723-555EBFC1927E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2159DABC-8FF4-4114-8115-FDFA21984891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="集成_RISCV_TOP" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="122">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -347,10 +347,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>范围是{{32,32,64}}*8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MEM_DAT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -480,6 +476,51 @@
   </si>
   <si>
     <t>verification_sig_{{i}}_tie0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RST_LANE</t>
+  </si>
+  <si>
+    <t>CLK_LANE</t>
+  </si>
+  <si>
+    <t>`GLB_RST_LANE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模块名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例化名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例化次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA-&gt;ready_test_process</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test_bus2_{{j}}_valid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA-&gt;1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROJECT_PERSONAL_MEM_DAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RISCV_CRG</t>
+  </si>
+  <si>
+    <t>范围是{{6,6,4}}*8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -523,11 +564,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -811,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH27"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="9.33203125" customWidth="1"/>
@@ -819,56 +861,64 @@
     <col min="12" max="12" width="10.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="B1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="L1" s="2" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="L1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="M1" s="3"/>
+      <c r="N1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="2"/>
+      <c r="O1" s="3"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T1" s="2"/>
+      <c r="T1" s="3"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Z1" s="2"/>
-      <c r="AC1" s="2" t="s">
+      <c r="X1" s="3"/>
+      <c r="AA1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="2"/>
-      <c r="AG1" s="2" t="s">
+      <c r="AB1" s="3"/>
+      <c r="AE1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="2"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.4">
+      <c r="AF1" s="3"/>
+      <c r="AH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -917,668 +967,717 @@
       <c r="T2" t="s">
         <v>2</v>
       </c>
+      <c r="V2" t="s">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1</v>
+      </c>
       <c r="X2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="s">
         <v>0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
         <v>2</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>0</v>
       </c>
-      <c r="AC2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
         <v>2</v>
       </c>
-      <c r="AF2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>1</v>
-      </c>
       <c r="AH2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A4" s="3"/>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" t="s">
+        <v>5</v>
+      </c>
+      <c r="S5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="W5" t="s">
+        <v>21</v>
+      </c>
+      <c r="X5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A6" s="3"/>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>100</v>
+      </c>
+      <c r="R6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="3"/>
+      <c r="W6" t="s">
+        <v>23</v>
+      </c>
+      <c r="X6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="3"/>
+      <c r="AA6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="3"/>
+      <c r="AE6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A7" s="3"/>
+      <c r="B7" t="s">
         <v>89</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" t="s">
+        <v>5</v>
+      </c>
+      <c r="V7" s="3"/>
+      <c r="W7" t="s">
+        <v>24</v>
+      </c>
+      <c r="X7" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z7" s="3"/>
+      <c r="AA7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD7" s="3"/>
+      <c r="AE7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A8" s="3"/>
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="R3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S3" t="s">
-        <v>96</v>
-      </c>
-      <c r="T3" t="s">
-        <v>20</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
-      <c r="B4" t="s">
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" t="s">
+        <v>5</v>
+      </c>
+      <c r="V8" s="3"/>
+      <c r="W8" t="s">
+        <v>25</v>
+      </c>
+      <c r="X8" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z8" s="3"/>
+      <c r="AA8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD8" s="3"/>
+      <c r="AE8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="K9" s="3"/>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3"/>
+      <c r="W9" t="s">
+        <v>26</v>
+      </c>
+      <c r="X9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z9" s="3"/>
+      <c r="AA9" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD9" s="3"/>
+      <c r="AE9" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3"/>
+      <c r="W10" t="s">
+        <v>26</v>
+      </c>
+      <c r="X10" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z10" s="3"/>
+      <c r="AA10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD10" s="3"/>
+      <c r="AE10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A11" s="3"/>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A12" s="3"/>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" t="s">
         <v>91</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>101</v>
-      </c>
-      <c r="R4" t="s">
-        <v>20</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="L12" t="s">
+        <v>92</v>
+      </c>
+      <c r="M12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A13" s="3"/>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" t="s">
         <v>102</v>
       </c>
-      <c r="X4" s="2"/>
-      <c r="Y4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB4" s="2"/>
-      <c r="AC4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF4" s="2"/>
-      <c r="AG4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A5" s="2"/>
-      <c r="B5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" t="s">
-        <v>5</v>
-      </c>
-      <c r="X5" s="2"/>
-      <c r="Y5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB5" s="2"/>
-      <c r="AC5" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF5" s="2"/>
-      <c r="AG5" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A6" s="2"/>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X6" s="2"/>
-      <c r="Y6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB6" s="2"/>
-      <c r="AC6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF6" s="2"/>
-      <c r="AG6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="K7" s="2"/>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X7" s="2"/>
-      <c r="Y7" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB7" s="2"/>
-      <c r="AC7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF7" s="2"/>
-      <c r="AG7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>20</v>
-      </c>
-      <c r="N8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8" t="s">
-        <v>5</v>
-      </c>
-      <c r="X8" s="2"/>
-      <c r="Y8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB8" s="2"/>
-      <c r="AC8" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF8" s="2"/>
-      <c r="AG8" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" t="s">
-        <v>56</v>
-      </c>
-      <c r="O9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A10" s="2"/>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" t="s">
-        <v>92</v>
-      </c>
-      <c r="L10" t="s">
-        <v>93</v>
-      </c>
-      <c r="M10" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="M13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" t="s">
+        <v>102</v>
+      </c>
+      <c r="O13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A14" s="3"/>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="3"/>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" s="3"/>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A11" s="2"/>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K11" t="s">
-        <v>104</v>
-      </c>
-      <c r="L11" t="s">
-        <v>103</v>
-      </c>
-      <c r="M11" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A12" s="2"/>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="2"/>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="2"/>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="D22" t="s">
         <v>52</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E22" t="s">
         <v>54</v>
       </c>
-      <c r="D20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" t="s">
         <v>60</v>
       </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" t="s">
         <v>60</v>
       </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="2"/>
-      <c r="B23" t="s">
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="3"/>
+      <c r="B25" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
         <v>61</v>
       </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
+      <c r="E25" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3"/>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="3"/>
+      <c r="B29" t="s">
         <v>81</v>
       </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" t="s">
-        <v>72</v>
-      </c>
-      <c r="I26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="2"/>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" t="s">
-        <v>54</v>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AB3:AB8"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AF3:AF8"/>
-    <mergeCell ref="A8:A12"/>
+  <mergeCells count="21">
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="V5:V10"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="Z5:Z10"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AD5:AD10"/>
+    <mergeCell ref="A10:A14"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="K3:K8"/>
+    <mergeCell ref="K5:K10"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="X3:X8"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A3:A6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{202D62A6-CB45-4A21-B036-6EE2427F8DDC}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="23.06640625" customWidth="1"/>
@@ -1619,355 +1718,379 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="3"/>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
         <v>39</v>
       </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
-      <c r="B4" t="s">
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="3"/>
+      <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>40</v>
       </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <v>64</v>
       </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="2"/>
-      <c r="B7" t="s">
+      <c r="F8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9" s="3"/>
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>41</v>
       </c>
-      <c r="E7">
+      <c r="E9">
         <v>64</v>
       </c>
-      <c r="F7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="2"/>
-      <c r="B8" t="s">
+      <c r="F9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10" s="3"/>
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
-      <c r="B9" t="s">
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11" s="3"/>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="2"/>
-      <c r="B10" t="s">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12" s="3"/>
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
-      <c r="B15" t="s">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
+      <c r="B17" t="s">
         <v>23</v>
       </c>
-      <c r="D15">
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="F15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="2"/>
-      <c r="B16" t="s">
+      <c r="F17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="D16">
+      <c r="D18">
         <v>3</v>
       </c>
-      <c r="F16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="2"/>
-      <c r="B17" t="s">
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="3"/>
+      <c r="B19" t="s">
         <v>25</v>
       </c>
-      <c r="D17">
+      <c r="D19">
         <v>4</v>
       </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="2"/>
-      <c r="B18" t="s">
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" s="3"/>
+      <c r="B20" t="s">
         <v>26</v>
       </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="2"/>
-      <c r="B19" t="s">
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="3"/>
+      <c r="B21" t="s">
         <v>43</v>
       </c>
-      <c r="D19">
+      <c r="D21">
         <v>6</v>
       </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B23" t="s">
         <v>44</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" t="s">
         <v>86</v>
       </c>
-      <c r="E21" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="F23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="2"/>
-      <c r="B22" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="3"/>
+      <c r="B24" t="s">
         <v>45</v>
       </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="2"/>
-      <c r="B23" t="s">
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="3"/>
+      <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
         <v>51</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B27" t="s">
         <v>52</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" t="s">
         <v>53</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="2" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
         <v>60</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" t="s">
         <v>48</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E29" t="s">
         <v>69</v>
       </c>
-      <c r="F27" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="F29" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="2"/>
-      <c r="B28" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30" s="3"/>
+      <c r="B30" t="s">
         <v>61</v>
       </c>
-      <c r="F28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="2"/>
-      <c r="B29" t="s">
+      <c r="F30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" s="3"/>
+      <c r="B31" t="s">
         <v>62</v>
       </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>72</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>73</v>
       </c>
-      <c r="E31">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="2"/>
-      <c r="B32" t="s">
+      <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" s="3"/>
+      <c r="B34" t="s">
         <v>74</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" t="s">
         <v>79</v>
       </c>
-      <c r="E32" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
         <v>109</v>
       </c>
-      <c r="E34">
+      <c r="D36" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36">
         <v>32</v>
       </c>
-      <c r="F34" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" t="s">
-        <v>106</v>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A31:A32"/>
+  <mergeCells count="7">
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A29:A31"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2017,46 +2140,46 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
         <v>85</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>87</v>
       </c>
       <c r="I3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3"/>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2066,12 +2189,12 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3"/>
       <c r="B7" t="s">
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2081,7 +2204,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B9" t="s">
@@ -2095,7 +2218,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="2"/>
+      <c r="A10" s="3"/>
       <c r="B10" t="s">
         <v>10</v>
       </c>
@@ -2124,7 +2247,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B14" t="s">
@@ -2138,7 +2261,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
+      <c r="A15" s="3"/>
       <c r="B15" t="s">
         <v>23</v>
       </c>
@@ -2150,7 +2273,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3"/>
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -2162,7 +2285,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="2"/>
+      <c r="A17" s="3"/>
       <c r="B17" t="s">
         <v>25</v>
       </c>
@@ -2174,7 +2297,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="2"/>
+      <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>26</v>
       </c>
@@ -2186,7 +2309,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3"/>
       <c r="B19" t="s">
         <v>26</v>
       </c>
@@ -2198,7 +2321,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B21" t="s">
@@ -2215,7 +2338,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="2"/>
+      <c r="A22" s="3"/>
       <c r="B22" t="s">
         <v>15</v>
       </c>
@@ -2227,7 +2350,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="2"/>
+      <c r="A23" s="3"/>
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -2239,7 +2362,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
+      <c r="A24" s="3"/>
       <c r="B24" t="s">
         <v>17</v>
       </c>
@@ -2251,7 +2374,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="2"/>
+      <c r="A25" s="3"/>
       <c r="B25" t="s">
         <v>18</v>
       </c>
@@ -2263,7 +2386,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="2"/>
+      <c r="A26" s="3"/>
       <c r="B26" t="s">
         <v>19</v>
       </c>
@@ -2275,14 +2398,14 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
@@ -2292,7 +2415,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="2"/>
+      <c r="A29" s="3"/>
       <c r="B29" t="s">
         <v>45</v>
       </c>
@@ -2304,7 +2427,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="2"/>
+      <c r="A30" s="3"/>
       <c r="B30" t="s">
         <v>46</v>
       </c>
@@ -2330,7 +2453,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B34" t="s">
@@ -2347,7 +2470,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="2"/>
+      <c r="A35" s="3"/>
       <c r="B35" t="s">
         <v>66</v>
       </c>
@@ -2362,14 +2485,14 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B37" t="s">
         <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
         <v>70</v>
@@ -2382,7 +2505,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="2"/>
+      <c r="A38" s="3"/>
       <c r="B38" t="s">
         <v>61</v>
       </c>
@@ -2391,7 +2514,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="2"/>
+      <c r="A39" s="3"/>
       <c r="B39" t="s">
         <v>62</v>
       </c>
@@ -2401,13 +2524,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
         <v>92</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
         <v>93</v>
-      </c>
-      <c r="D41" t="s">
-        <v>94</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
@@ -2415,13 +2538,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E43">
         <v>32</v>
@@ -2430,7 +2553,7 @@
         <v>20</v>
       </c>
       <c r="I43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2489,7 +2612,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
@@ -2506,7 +2629,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
       <c r="B4" t="s">
         <v>38</v>
       </c>
@@ -2521,7 +2644,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
@@ -2541,7 +2664,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3"/>
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -2559,7 +2682,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="2"/>
+      <c r="A8" s="3"/>
       <c r="B8" t="s">
         <v>9</v>
       </c>
@@ -2574,7 +2697,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3"/>
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -2609,14 +2732,14 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -2626,7 +2749,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="2"/>
+      <c r="A14" s="3"/>
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -2638,7 +2761,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
+      <c r="A15" s="3"/>
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -2650,7 +2773,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3"/>
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -2662,7 +2785,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="2"/>
+      <c r="A17" s="3"/>
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -2674,7 +2797,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="2"/>
+      <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -2686,7 +2809,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
@@ -2700,7 +2823,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="2"/>
+      <c r="A21" s="3"/>
       <c r="B21" t="s">
         <v>23</v>
       </c>
@@ -2712,7 +2835,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="2"/>
+      <c r="A22" s="3"/>
       <c r="B22" t="s">
         <v>24</v>
       </c>
@@ -2724,7 +2847,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="2"/>
+      <c r="A23" s="3"/>
       <c r="B23" t="s">
         <v>25</v>
       </c>
@@ -2736,7 +2859,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
+      <c r="A24" s="3"/>
       <c r="B24" t="s">
         <v>26</v>
       </c>
@@ -2748,7 +2871,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="2"/>
+      <c r="A25" s="3"/>
       <c r="B25" t="s">
         <v>26</v>
       </c>
@@ -2760,17 +2883,17 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
@@ -2780,7 +2903,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="2"/>
+      <c r="A28" s="3"/>
       <c r="B28" t="s">
         <v>45</v>
       </c>
@@ -2792,7 +2915,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="2"/>
+      <c r="A29" s="3"/>
       <c r="B29" t="s">
         <v>46</v>
       </c>
@@ -2811,7 +2934,7 @@
         <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
         <v>57</v>
@@ -2822,13 +2945,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
@@ -2836,19 +2959,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" t="s">
         <v>104</v>
       </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" t="s">
         <v>105</v>
-      </c>
-      <c r="F35" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2871,7 +2994,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H1" t="s">
         <v>35</v>
@@ -2904,7 +3027,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B3" t="s">
@@ -2918,7 +3041,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
       <c r="B4" t="s">
         <v>74</v>
       </c>
@@ -2926,10 +3049,10 @@
         <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I4" t="s">
         <v>75</v>
@@ -2951,7 +3074,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
@@ -2984,8 +3107,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>98</v>
+      <c r="A3" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -2998,18 +3121,18 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
         <v>99</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
